--- a/mydata.xlsx
+++ b/mydata.xlsx
@@ -5,15 +5,15 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Haw\logs\dev\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HW\Technology\Log books\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3D9748BA-42C5-4EA6-B8B0-590EBDAF656F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A79DD3-F4E1-415A-B5EF-EB8242C081B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EFA04CBE-C006-4570-B4A5-EE8A17ABFE03}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="ship" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>

--- a/mydata.xlsx
+++ b/mydata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\HW\Technology\Log books\dev\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26A79DD3-F4E1-415A-B5EF-EB8242C081B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03B5914A-3619-41B4-A7D5-20299687D7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{EFA04CBE-C006-4570-B4A5-EE8A17ABFE03}"/>
   </bookViews>
@@ -412,8 +412,7 @@
   <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" customWidth="1"/>
-    <col min="2" max="2" width="14" style="1" customWidth="1"/>
+    <col min="1" max="1" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
